--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123358358</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>123353344</v>
       </c>
       <c r="B3" t="n">
-        <v>58156</v>
+        <v>58159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>123354795</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358358</v>
+        <v>123354795</v>
       </c>
       <c r="B2" t="n">
         <v>57851</v>
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bingen, Bingen, Dls</t>
+          <t>Boden, Boden, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345094</v>
+        <v>344967</v>
       </c>
       <c r="R2" t="n">
-        <v>6535573</v>
+        <v>6535416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
+          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +788,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123353344</v>
+        <v>123358358</v>
       </c>
       <c r="B3" t="n">
-        <v>58159</v>
+        <v>57851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344931</v>
+        <v>345094</v>
       </c>
       <c r="R3" t="n">
-        <v>6535478</v>
+        <v>6535573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123354795</v>
+        <v>123353344</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>58159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344967</v>
+        <v>344931</v>
       </c>
       <c r="R4" t="n">
-        <v>6535416</v>
+        <v>6535478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123354795</v>
+        <v>123353344</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>58159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344967</v>
+        <v>344931</v>
       </c>
       <c r="R2" t="n">
-        <v>6535416</v>
+        <v>6535478</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353344</v>
+        <v>123354795</v>
       </c>
       <c r="B4" t="n">
-        <v>58159</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344931</v>
+        <v>344967</v>
       </c>
       <c r="R4" t="n">
-        <v>6535478</v>
+        <v>6535416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123353344</v>
+        <v>123358358</v>
       </c>
       <c r="B2" t="n">
-        <v>58159</v>
+        <v>57857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344931</v>
+        <v>345094</v>
       </c>
       <c r="R2" t="n">
-        <v>6535478</v>
+        <v>6535573</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +788,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358358</v>
+        <v>123353344</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>58165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bingen, Bingen, Dls</t>
+          <t>Boden, Boden, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345094</v>
+        <v>344931</v>
       </c>
       <c r="R3" t="n">
-        <v>6535573</v>
+        <v>6535478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,7 +940,7 @@
         <v>123354795</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358358</v>
+        <v>123353344</v>
       </c>
       <c r="B2" t="n">
-        <v>57857</v>
+        <v>58165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bingen, Bingen, Dls</t>
+          <t>Boden, Boden, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345094</v>
+        <v>344931</v>
       </c>
       <c r="R2" t="n">
-        <v>6535573</v>
+        <v>6535478</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +788,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123353344</v>
+        <v>123358358</v>
       </c>
       <c r="B3" t="n">
-        <v>58165</v>
+        <v>57857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344931</v>
+        <v>345094</v>
       </c>
       <c r="R3" t="n">
-        <v>6535478</v>
+        <v>6535573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123353344</v>
+        <v>123358358</v>
       </c>
       <c r="B2" t="n">
-        <v>58165</v>
+        <v>57857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344931</v>
+        <v>345094</v>
       </c>
       <c r="R2" t="n">
-        <v>6535478</v>
+        <v>6535573</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +788,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358358</v>
+        <v>123353344</v>
       </c>
       <c r="B3" t="n">
-        <v>57857</v>
+        <v>58165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bingen, Bingen, Dls</t>
+          <t>Boden, Boden, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345094</v>
+        <v>344931</v>
       </c>
       <c r="R3" t="n">
-        <v>6535573</v>
+        <v>6535478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123358358</v>
       </c>
       <c r="B2" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123353344</v>
+        <v>123354795</v>
       </c>
       <c r="B3" t="n">
-        <v>58165</v>
+        <v>57860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344931</v>
+        <v>344967</v>
       </c>
       <c r="R3" t="n">
-        <v>6535478</v>
+        <v>6535416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123354795</v>
+        <v>123353344</v>
       </c>
       <c r="B4" t="n">
-        <v>57857</v>
+        <v>58168</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344967</v>
+        <v>344931</v>
       </c>
       <c r="R4" t="n">
-        <v>6535416</v>
+        <v>6535478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358358</v>
+        <v>123353344</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bingen, Bingen, Dls</t>
+          <t>Boden, Boden, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345094</v>
+        <v>344931</v>
       </c>
       <c r="R2" t="n">
-        <v>6535573</v>
+        <v>6535478</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +788,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123354795</v>
+        <v>123358358</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -861,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344967</v>
+        <v>345094</v>
       </c>
       <c r="R3" t="n">
-        <v>6535416</v>
+        <v>6535573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
+          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353344</v>
+        <v>123354795</v>
       </c>
       <c r="B4" t="n">
-        <v>58168</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344931</v>
+        <v>344967</v>
       </c>
       <c r="R4" t="n">
-        <v>6535478</v>
+        <v>6535416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123353344</v>
+        <v>123354795</v>
       </c>
       <c r="B2" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344931</v>
+        <v>344967</v>
       </c>
       <c r="R2" t="n">
-        <v>6535478</v>
+        <v>6535416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123354795</v>
+        <v>123353344</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344967</v>
+        <v>344931</v>
       </c>
       <c r="R4" t="n">
-        <v>6535416</v>
+        <v>6535478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358358</v>
+        <v>123353344</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bingen, Bingen, Dls</t>
+          <t>Boden, Boden, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345094</v>
+        <v>344931</v>
       </c>
       <c r="R3" t="n">
-        <v>6535573</v>
+        <v>6535478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353344</v>
+        <v>123358358</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -992,14 +992,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344931</v>
+        <v>345094</v>
       </c>
       <c r="R4" t="n">
-        <v>6535478</v>
+        <v>6535573</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123354795</v>
+        <v>123358358</v>
       </c>
       <c r="B2" t="n">
         <v>57861</v>
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344967</v>
+        <v>345094</v>
       </c>
       <c r="R2" t="n">
-        <v>6535416</v>
+        <v>6535573</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
+          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +788,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123353344</v>
+        <v>123354795</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344931</v>
+        <v>344967</v>
       </c>
       <c r="R3" t="n">
-        <v>6535478</v>
+        <v>6535416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123358358</v>
+        <v>123353344</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -992,14 +992,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bingen, Bingen, Dls</t>
+          <t>Boden, Boden, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345094</v>
+        <v>344931</v>
       </c>
       <c r="R4" t="n">
-        <v>6535573</v>
+        <v>6535478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358358</v>
+        <v>123353344</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bingen, Bingen, Dls</t>
+          <t>Boden, Boden, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345094</v>
+        <v>344931</v>
       </c>
       <c r="R2" t="n">
-        <v>6535573</v>
+        <v>6535478</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +788,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123354795</v>
+        <v>123358358</v>
       </c>
       <c r="B3" t="n">
         <v>57861</v>
@@ -861,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344967</v>
+        <v>345094</v>
       </c>
       <c r="R3" t="n">
-        <v>6535416</v>
+        <v>6535573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
+          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353344</v>
+        <v>123354795</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344931</v>
+        <v>344967</v>
       </c>
       <c r="R4" t="n">
-        <v>6535478</v>
+        <v>6535416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123354795</v>
+        <v>123358022</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,19 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -730,17 +716,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344967</v>
+        <v>345132</v>
       </c>
       <c r="R2" t="n">
-        <v>6535416</v>
+        <v>6535541</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358358</v>
+        <v>123354795</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -861,14 +842,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bingen, Bingen, Dls</t>
+          <t>Boden, Boden, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345094</v>
+        <v>344967</v>
       </c>
       <c r="R3" t="n">
-        <v>6535573</v>
+        <v>6535416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +886,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
+          <t>I flerskiktad barrskog med gran, tall, björk och ek i en mossikartad blandning med partier som utgörs av impediment med gles tallskog och sluttande blockmark med gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +900,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,15 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353344</v>
+        <v>123358358</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -992,14 +968,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Boden, Boden, Dls</t>
+          <t>Bingen, Bingen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344931</v>
+        <v>345094</v>
       </c>
       <c r="R4" t="n">
-        <v>6535478</v>
+        <v>6535573</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+          <t>Fyndplatsen finns i högväxt äldre granskog som bitvis är flerskiktad och ligger på sluttande blockig mosstäckt mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1026,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1065,6 +1041,253 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123353344</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Boden, Boden, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>344931</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6535478</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I flerskiktad barrskog med gran, tall och björk i en mossikartad blandning med partier som utgörs av impediment med gles tallskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123358081</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bingen, Bingen, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>345149</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6535556</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1582-2022 artfynd.xlsx
+++ b/artfynd/A 1582-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123354795</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123358022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123358358</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1167,6 +1187,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123353344</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1288,8 +1313,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123358081</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>